--- a/excel_templates/手机卡表.xlsx
+++ b/excel_templates/手机卡表.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13986903203.0</t>
+          <t>13986903203</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
